--- a/templates/입력1_병동인력표_2026-09.xlsx
+++ b/templates/입력1_병동인력표_2026-09.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,18 +31,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000F6E6B"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,19 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,139 +426,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>입력① 병동인력표 — 양식 안내</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이 파일은 실제 42명(파트장 1 · A팀 39 · B팀 2) 규모 병동 데이터를 바탕으로 만든 예시입니다. 이름은 개인정보 보호를 위해 숫자로 익명화돼 있으니, 실제 이름으로 바꿔서 쓰세요.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>이 파일은 실제 42명(파트장 1 · A팀 39 · B팀 2) 규모 병동 데이터를 바탕으로 만든 예시입니다. 이름은 개인정보 보호를 위해 숫자로 익명화돼 있으니, 실제 이름으로 바꿔서 쓰세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>시트 구성 (① 설정 · ② 인원 · ③ 최소인력 3개는 필수, B팀은 선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>① 설정 — 항목|값 두 칸짜리 표. 아래 항목들을 채웁니다:</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>시트 구성 (① 설정 · ② 인원 · ③ 최소인력 3개는 필수, B팀은 선택)</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 병동명 — 다운로드 파일명 등에 쓰임(비워도 됨)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>① 설정 — 항목|값 두 칸짜리 표. 아래 항목들을 채웁니다:</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 연도, 월 — 근무표를 만들 대상 연월 (필수)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 병동명 — 다운로드 파일명 등에 쓰임(비워도 됨)</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 월최대야간 — 일반 간호사 한 명이 한 달에 설 수 있는 야간 근무 상한(기본 6)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 연도, 월 — 근무표를 만들 대상 연월 (필수)</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 공휴일·대체공휴일·월신청상한은 이 표에 넣지 않습니다 — 공휴일은 코드가 2040년까지 자동으로 계산해서 채우고(설날·추석 등 음력 명절, 대체공휴일 규정까지 반영), 월신청상한은 고정값을 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 월최대야간 — 일반 간호사 한 명이 한 달에 설 수 있는 야간 근무 상한(기본 6)</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · NK인원수, 심화과정대상은 선택 항목, 비워도 자동 처리됨</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 공휴일 — 'YYYY-MM-DD' 형식, 콤마로 여러 개 (선택, 비우면 자동 계산된 법정공휴일만 반영)</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>② 인원 — 순번 | 이름 | 직급 | 숙련도 | 가능근무 | 비고</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 대체공휴일, 월신청상한, NK인원수, 심화과정대상 — 전부 선택 항목, 비워도 자동 처리됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 직급: 파트장(항상 8A 상근) / 리더 / 간호사</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 숙련도: Lv1~Lv5 (레벨이 높을수록 '고랩' 판정에 유리 — 파트별 상대 기준으로 자동 계산됨)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>② 인원 — 순번 | 이름 | 직급 | 숙련도 | 가능근무 | 비고</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 가능근무: 콤마로 구분해서 적습니다. 예) D,E,N,prn / 야간전담이면 NK 하나만</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 직급: 파트장(항상 8A 상근) / 리더 / 간호사</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 비고: '야간전담'이라고 적으면 NK 전담 간호사로 자동 인식, '임부'나 '야간금지'라고 적으면 야간 배정에서 자동 제외됩니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 숙련도: Lv1~Lv5 (레벨이 높을수록 '고랩' 판정에 유리 — 파트별 상대 기준으로 자동 계산됨)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>③ 최소인력 — 근무(D/E/N/prn) × 평일/토요일/일요일·공휴일 별 필요 최소 인원수.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 가능근무: 콤마로 구분해서 적습니다. 예) D,E,N,prn / 야간전담이면 NK 하나만</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 비고: '야간전담'이라고 적으면 NK 전담 간호사로 자동 인식, '임부'나 '야간금지'라고 적으면 야간 배정에서 자동 제외됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>③ 최소인력 — 근무(D/E/N/prn) × 평일/토요일/일요일·공휴일 별 필요 최소 인원수.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>선택: B팀(신입) — 이름 한 줄씩만. 근무 배정에는 전혀 관여하지 않고, 출력 근무표에
 'B' 구분란에 이름만 표시됩니다 — 파트장이 직접 배정하세요.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>이 파일만으로도 근무표 생성은 가능합니다</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>신청(원티드)과 전월이월은 이 파일 안에 시트로 같이 넣을 수도 있지만, 화면의 입력②(전월 확정 근무표)와 입력③(원티드표)으로 따로 올리는 편이 관리하기 더 편합니다.</t>
         </is>
@@ -597,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -651,35 +624,6 @@
       </c>
       <c r="B5" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>월신청상한</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>공휴일</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-24, 2026-09-25, 2026-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>대체공휴일</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/templates/입력1_병동인력표_2026-09.xlsx
+++ b/templates/입력1_병동인력표_2026-09.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -491,69 +491,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · NK인원수, 심화과정대상은 선택 항목, 비워도 자동 처리됨</t>
+          <t xml:space="preserve">   · 연속근무제한 — 연속으로 일할 수 있는 최대 일수(기본 5). 병동 사정에 맞게 4 등으로 낮출 수 있음(비워도 기본 5로 처리됨)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>② 인원 — 순번 | 이름 | 직급 | 숙련도 | 가능근무 | 비고</t>
+          <t xml:space="preserve">   · NK인원수, 심화과정대상은 선택 항목, 비워도 자동 처리됨</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 직급: 파트장(항상 8A 상근) / 리더 / 간호사</t>
+          <t>② 인원 — 순번 | 이름 | 직급 | 숙련도 | 가능근무 | 비고</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 숙련도: Lv1~Lv5 (레벨이 높을수록 '고랩' 판정에 유리 — 파트별 상대 기준으로 자동 계산됨)</t>
+          <t xml:space="preserve">   · 직급: 파트장(항상 8A 상근) / 리더 / 간호사</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 가능근무: 콤마로 구분해서 적습니다. 예) D,E,N,prn / 야간전담이면 NK 하나만</t>
+          <t xml:space="preserve">   · 숙련도: Lv1~Lv5 (레벨이 높을수록 '고랩' 판정에 유리 — 파트별 상대 기준으로 자동 계산됨)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 비고: '야간전담'이라고 적으면 NK 전담 간호사로 자동 인식, '임부'나 '야간금지'라고 적으면 야간 배정에서 자동 제외됩니다.</t>
+          <t xml:space="preserve">   · 가능근무: 콤마로 구분해서 적습니다. 예) D,E,N,prn / 야간전담이면 NK 하나만</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>③ 최소인력 — 근무(D/E/N/prn) × 평일/토요일/일요일·공휴일 별 필요 최소 인원수.</t>
+          <t xml:space="preserve">   · 비고: '야간전담'이라고 적으면 NK 전담 간호사로 자동 인식, '임부'나 '야간금지'라고 적으면 야간 배정에서 자동 제외됩니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>③ 최소인력 — 근무(D/E/N/prn) × 평일/토요일/일요일·공휴일 별 필요 최소 인원수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>선택: B팀(신입) — 이름 한 줄씩만. 근무 배정에는 전혀 관여하지 않고, 출력 근무표에
 'B' 구분란에 이름만 표시됩니다 — 파트장이 직접 배정하세요.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>이 파일만으로도 근무표 생성은 가능합니다</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t>이 파일만으로도 근무표 생성은 가능합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>신청(원티드)과 전월이월은 이 파일 안에 시트로 같이 넣을 수도 있지만, 화면의 입력②(전월 확정 근무표)와 입력③(원티드표)으로 따로 올리는 편이 관리하기 더 편합니다.</t>
         </is>
@@ -570,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -624,6 +631,16 @@
       </c>
       <c r="B5" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>연속근무제한</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/templates/입력1_병동인력표_2026-09.xlsx
+++ b/templates/입력1_병동인력표_2026-09.xlsx
@@ -1867,14 +1867,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>42</t>
         </is>
       </c>
     </row>
